--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eirar\Polla\Pauta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos Codex\08 Imput Mundial\pautas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EE4CA4-A7C9-434A-A69B-1AF63D1A92FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C547B6FF-8ACA-45FE-BDB0-2814BE58B285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
   <si>
     <t>Partido 1</t>
   </si>
@@ -72,6 +72,54 @@
   </si>
   <si>
     <t>Partido 8</t>
+  </si>
+  <si>
+    <t>Canadá</t>
+  </si>
+  <si>
+    <t>Marruecos</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Francia</t>
+  </si>
+  <si>
+    <t>Brasil</t>
+  </si>
+  <si>
+    <t>Noruega</t>
+  </si>
+  <si>
+    <t>México</t>
+  </si>
+  <si>
+    <t>Inglaterra</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>España</t>
+  </si>
+  <si>
+    <t>Estados Unidos</t>
+  </si>
+  <si>
+    <t>Bélgica</t>
+  </si>
+  <si>
+    <t>Suiza</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Egipto</t>
   </si>
 </sst>
 </file>
@@ -558,18 +606,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831F1176-9B5F-4509-AEB9-C4D2AF7AA58E}">
   <dimension ref="B1:I138"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.53125" customWidth="1"/>
-    <col min="2" max="2" width="14.46484375" customWidth="1"/>
-    <col min="3" max="3" width="3.53125" customWidth="1"/>
-    <col min="4" max="4" width="14.796875" customWidth="1"/>
-    <col min="8" max="8" width="13.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" customWidth="1"/>
+    <col min="3" max="3" width="3.54296875" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.1796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.08984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
@@ -577,27 +625,31 @@
       <c r="D2" s="10"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Canadá</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="1"/>
+    <row r="3" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="H3" s="5" t="str">
         <f>"Pasa "&amp; D3</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Marruecos</v>
       </c>
       <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" s="6"/>
       <c r="C4" s="7"/>
       <c r="D4" s="3"/>
@@ -605,8 +657,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
@@ -614,27 +666,31 @@
       <c r="D6" s="10"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Paraguay</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="1"/>
+    <row r="7" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="H7" s="5" t="str">
         <f>"Pasa "&amp; D7</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Francia</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="6"/>
       <c r="C8" s="7"/>
       <c r="D8" s="3"/>
@@ -642,8 +698,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="10" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
@@ -651,27 +707,31 @@
       <c r="D10" s="10"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Brasil</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B11" s="1"/>
+    <row r="11" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="C11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="H11" s="5" t="str">
         <f>"Pasa "&amp; D11</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Noruega</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" s="6"/>
       <c r="C12" s="7"/>
       <c r="D12" s="3"/>
@@ -679,8 +739,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="14" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
@@ -688,27 +748,31 @@
       <c r="D14" s="10"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa México</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B15" s="1"/>
+    <row r="15" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="C15" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="H15" s="5" t="str">
         <f>"Pasa "&amp; D15</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Inglaterra</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B16" s="6"/>
       <c r="C16" s="7"/>
       <c r="D16" s="3"/>
@@ -716,8 +780,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="18" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
@@ -725,27 +789,31 @@
       <c r="D18" s="10"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Portugal</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B19" s="1"/>
+    <row r="19" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="C19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="H19" s="5" t="str">
         <f>"Pasa "&amp; D19</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa España</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B20" s="6"/>
       <c r="C20" s="7"/>
       <c r="D20" s="3"/>
@@ -753,8 +821,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="22" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
@@ -762,27 +830,31 @@
       <c r="D22" s="10"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Estados Unidos</v>
       </c>
       <c r="I22" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B23" s="1"/>
+    <row r="23" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="H23" s="5" t="str">
         <f>"Pasa "&amp; D23</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Bélgica</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B24" s="6"/>
       <c r="C24" s="7"/>
       <c r="D24" s="3"/>
@@ -790,8 +862,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="26" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
@@ -799,27 +871,31 @@
       <c r="D26" s="10"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Argentina</v>
       </c>
       <c r="I26" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B27" s="1"/>
+    <row r="27" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="C27" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H27" s="5" t="str">
         <f>"Pasa "&amp; D27</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Egipto</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="3"/>
@@ -827,8 +903,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="30" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B30" s="8" t="s">
         <v>11</v>
       </c>
@@ -836,27 +912,31 @@
       <c r="D30" s="10"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Suiza</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B31" s="1"/>
+    <row r="31" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>24</v>
+      </c>
       <c r="C31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D31" s="2"/>
+      <c r="D31" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="H31" s="5" t="str">
         <f>"Pasa "&amp; D31</f>
-        <v xml:space="preserve">Pasa </v>
+        <v>Pasa Colombia</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B32" s="6"/>
       <c r="C32" s="7"/>
       <c r="D32" s="3"/>
@@ -864,427 +944,427 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H33"/>
       <c r="I33"/>
     </row>
-    <row r="34" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H34"/>
       <c r="I34"/>
     </row>
-    <row r="35" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H35"/>
       <c r="I35"/>
     </row>
-    <row r="36" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H36"/>
       <c r="I36"/>
     </row>
-    <row r="37" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H37"/>
       <c r="I37"/>
     </row>
-    <row r="38" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H38"/>
       <c r="I38"/>
     </row>
-    <row r="39" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H39"/>
       <c r="I39"/>
     </row>
-    <row r="40" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H40"/>
       <c r="I40"/>
     </row>
-    <row r="41" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H41"/>
       <c r="I41"/>
     </row>
-    <row r="42" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H42"/>
       <c r="I42"/>
     </row>
-    <row r="43" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H43"/>
       <c r="I43"/>
     </row>
-    <row r="44" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H44"/>
       <c r="I44"/>
     </row>
-    <row r="45" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H45"/>
       <c r="I45"/>
     </row>
-    <row r="46" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H46"/>
       <c r="I46"/>
     </row>
-    <row r="47" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H47"/>
       <c r="I47"/>
     </row>
-    <row r="48" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H48"/>
       <c r="I48"/>
     </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H49"/>
       <c r="I49"/>
     </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H50"/>
       <c r="I50"/>
     </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H51"/>
       <c r="I51"/>
     </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H52"/>
       <c r="I52"/>
     </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H53"/>
       <c r="I53"/>
     </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H54"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H55"/>
       <c r="I55"/>
     </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H56"/>
       <c r="I56"/>
     </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H57"/>
       <c r="I57"/>
     </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H58"/>
       <c r="I58"/>
     </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H59"/>
       <c r="I59"/>
     </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H60"/>
       <c r="I60"/>
     </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H61"/>
       <c r="I61"/>
     </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H62"/>
       <c r="I62"/>
     </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H63"/>
       <c r="I63"/>
     </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H64"/>
       <c r="I64"/>
     </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H65"/>
       <c r="I65"/>
     </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H66"/>
       <c r="I66"/>
     </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H67"/>
       <c r="I67"/>
     </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H68"/>
       <c r="I68"/>
     </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H69"/>
       <c r="I69"/>
     </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H70"/>
       <c r="I70"/>
     </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H71"/>
       <c r="I71"/>
     </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H72"/>
       <c r="I72"/>
     </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H73"/>
       <c r="I73"/>
     </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H74"/>
       <c r="I74"/>
     </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H75"/>
       <c r="I75"/>
     </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H76"/>
       <c r="I76"/>
     </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H77"/>
       <c r="I77"/>
     </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H78"/>
       <c r="I78"/>
     </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H79"/>
       <c r="I79"/>
     </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H80"/>
       <c r="I80"/>
     </row>
-    <row r="81" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H81"/>
       <c r="I81"/>
     </row>
-    <row r="82" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H82"/>
       <c r="I82"/>
     </row>
-    <row r="83" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H83"/>
       <c r="I83"/>
     </row>
-    <row r="84" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H84"/>
       <c r="I84"/>
     </row>
-    <row r="85" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H85"/>
       <c r="I85"/>
     </row>
-    <row r="86" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H86"/>
       <c r="I86"/>
     </row>
-    <row r="87" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H87"/>
       <c r="I87"/>
     </row>
-    <row r="88" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H88"/>
       <c r="I88"/>
     </row>
-    <row r="89" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="89" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H89"/>
       <c r="I89"/>
     </row>
-    <row r="90" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="90" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H90"/>
       <c r="I90"/>
     </row>
-    <row r="91" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="91" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H91"/>
       <c r="I91"/>
     </row>
-    <row r="92" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="92" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="93" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="94" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="95" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="96" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H96"/>
       <c r="I96"/>
     </row>
-    <row r="97" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="97" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H97"/>
       <c r="I97"/>
     </row>
-    <row r="98" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="98" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H98"/>
       <c r="I98"/>
     </row>
-    <row r="99" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="99" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H99"/>
       <c r="I99"/>
     </row>
-    <row r="100" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="100" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H100"/>
       <c r="I100"/>
     </row>
-    <row r="101" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="101" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H101"/>
       <c r="I101"/>
     </row>
-    <row r="102" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="102" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H102"/>
       <c r="I102"/>
     </row>
-    <row r="103" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="103" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H103"/>
       <c r="I103"/>
     </row>
-    <row r="104" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="104" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H104"/>
       <c r="I104"/>
     </row>
-    <row r="105" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="105" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H105"/>
       <c r="I105"/>
     </row>
-    <row r="106" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="106" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H106"/>
       <c r="I106"/>
     </row>
-    <row r="107" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="107" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H107"/>
       <c r="I107"/>
     </row>
-    <row r="108" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="108" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H108"/>
       <c r="I108"/>
     </row>
-    <row r="109" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="109" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H109"/>
       <c r="I109"/>
     </row>
-    <row r="110" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="110" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="111" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H111"/>
       <c r="I111"/>
     </row>
-    <row r="112" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="112" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H112"/>
       <c r="I112"/>
     </row>
-    <row r="113" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="113" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H113"/>
       <c r="I113"/>
     </row>
-    <row r="114" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="114" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H114"/>
       <c r="I114"/>
     </row>
-    <row r="115" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="115" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H115"/>
       <c r="I115"/>
     </row>
-    <row r="116" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="116" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H116"/>
       <c r="I116"/>
     </row>
-    <row r="117" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="117" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H117"/>
       <c r="I117"/>
     </row>
-    <row r="118" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="118" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H118"/>
       <c r="I118"/>
     </row>
-    <row r="119" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="119" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H119"/>
       <c r="I119"/>
     </row>
-    <row r="120" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="120" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H120"/>
       <c r="I120"/>
     </row>
-    <row r="121" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="121" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H121"/>
       <c r="I121"/>
     </row>
-    <row r="122" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="122" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H122"/>
       <c r="I122"/>
     </row>
-    <row r="123" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="123" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H123"/>
       <c r="I123"/>
     </row>
-    <row r="124" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="124" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H124"/>
       <c r="I124"/>
     </row>
-    <row r="125" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="125" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H125"/>
       <c r="I125"/>
     </row>
-    <row r="126" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="126" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H126"/>
       <c r="I126"/>
     </row>
-    <row r="127" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="127" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H127"/>
       <c r="I127"/>
     </row>
-    <row r="128" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="128" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H128"/>
       <c r="I128"/>
     </row>
-    <row r="129" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="129" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H129"/>
       <c r="I129"/>
     </row>
-    <row r="130" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="130" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H130"/>
       <c r="I130"/>
     </row>
-    <row r="131" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="131" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H131"/>
       <c r="I131"/>
     </row>
-    <row r="132" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="132" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H132"/>
       <c r="I132"/>
     </row>
-    <row r="133" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="133" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H133"/>
       <c r="I133"/>
     </row>
-    <row r="134" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="134" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H134"/>
       <c r="I134"/>
     </row>
-    <row r="135" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="135" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H135"/>
       <c r="I135"/>
     </row>
-    <row r="136" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="136" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H136"/>
       <c r="I136"/>
     </row>
-    <row r="137" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="137" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H137"/>
       <c r="I137"/>
     </row>
-    <row r="138" spans="8:9" x14ac:dyDescent="0.45">
+    <row r="138" spans="8:9" x14ac:dyDescent="0.35">
       <c r="H138"/>
       <c r="I138"/>
     </row>

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos Codex\08 Imput Mundial\pautas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C547B6FF-8ACA-45FE-BDB0-2814BE58B285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -256,12 +256,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -269,6 +263,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -618,11 +618,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -650,8 +650,8 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="3"/>
       <c r="I4" s="5" t="s">
         <v>8</v>
@@ -659,11 +659,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -691,8 +691,8 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="3"/>
       <c r="I8" s="5" t="s">
         <v>8</v>
@@ -700,11 +700,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -732,8 +732,8 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="3"/>
       <c r="I12" s="5" t="s">
         <v>8</v>
@@ -741,11 +741,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -773,8 +773,8 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="3"/>
       <c r="I16" s="5" t="s">
         <v>8</v>
@@ -782,11 +782,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -814,8 +814,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>8</v>
@@ -823,11 +823,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -855,8 +855,8 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -864,11 +864,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -896,8 +896,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -905,11 +905,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -937,8 +937,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1370,22 +1370,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C547B6FF-8ACA-45FE-BDB0-2814BE58B285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBABDEBF-CAEC-4F56-8707-46161EC4C863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
   <si>
     <t>Partido 1</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Egipto</t>
+  </si>
+  <si>
+    <t>Pasa Canadá</t>
   </si>
 </sst>
 </file>
@@ -256,6 +259,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -263,12 +272,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -618,11 +621,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -650,20 +653,24 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="3"/>
+      <c r="B4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I4" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -691,8 +698,8 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="3"/>
       <c r="I8" s="5" t="s">
         <v>8</v>
@@ -700,11 +707,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -732,8 +739,8 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="3"/>
       <c r="I12" s="5" t="s">
         <v>8</v>
@@ -741,11 +748,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -773,8 +780,8 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="3"/>
       <c r="I16" s="5" t="s">
         <v>8</v>
@@ -782,11 +789,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -814,8 +821,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>8</v>
@@ -823,11 +830,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -855,8 +862,8 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -864,11 +871,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -896,8 +903,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -905,11 +912,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -937,8 +944,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1370,22 +1377,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -259,12 +259,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -272,6 +266,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -621,11 +621,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -653,10 +653,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -666,11 +666,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -698,8 +698,8 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="3"/>
       <c r="I8" s="5" t="s">
         <v>8</v>
@@ -707,11 +707,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -739,8 +739,8 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="3"/>
       <c r="I12" s="5" t="s">
         <v>8</v>
@@ -748,11 +748,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -780,8 +780,8 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="3"/>
       <c r="I16" s="5" t="s">
         <v>8</v>
@@ -789,11 +789,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -821,8 +821,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6"/>
-      <c r="C20" s="7"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>8</v>
@@ -830,11 +830,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -862,8 +862,8 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -871,11 +871,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -903,8 +903,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -912,11 +912,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -944,8 +944,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1377,22 +1377,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBABDEBF-CAEC-4F56-8707-46161EC4C863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DC639-8CF0-4B64-9E96-2CBA5D6EB4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -122,7 +122,7 @@
     <t>Egipto</t>
   </si>
   <si>
-    <t>Pasa Canadá</t>
+    <t>Pasa Marruecos</t>
   </si>
 </sst>
 </file>
@@ -259,6 +259,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -266,12 +272,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -621,11 +621,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -653,10 +653,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -666,11 +666,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -698,8 +698,8 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="3"/>
       <c r="I8" s="5" t="s">
         <v>8</v>
@@ -707,11 +707,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -739,8 +739,8 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
-      <c r="C12" s="10"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="3"/>
       <c r="I12" s="5" t="s">
         <v>8</v>
@@ -748,11 +748,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -780,8 +780,8 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="3"/>
       <c r="I16" s="5" t="s">
         <v>8</v>
@@ -789,11 +789,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -821,8 +821,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>8</v>
@@ -830,11 +830,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -862,8 +862,8 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -871,11 +871,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -903,8 +903,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -912,11 +912,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -944,8 +944,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1377,22 +1377,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DC639-8CF0-4B64-9E96-2CBA5D6EB4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67C38DD-7658-4DC0-BA5C-C326103F5FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t>Partido 1</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>Pasa Marruecos</t>
+  </si>
+  <si>
+    <t>Pasa Francia</t>
   </si>
 </sst>
 </file>
@@ -698,9 +701,13 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9"/>
+      <c r="B8" s="9" t="s">
+        <v>29</v>
+      </c>
       <c r="C8" s="10"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I8" s="5" t="s">
         <v>8</v>
       </c>

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67C38DD-7658-4DC0-BA5C-C326103F5FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390B15EA-8D87-4C3B-8AC8-B236072C4598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>Partido 1</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Pasa Francia</t>
+  </si>
+  <si>
+    <t>Pasa Noruega</t>
   </si>
 </sst>
 </file>
@@ -746,9 +749,13 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9"/>
+      <c r="B12" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="C12" s="10"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I12" s="5" t="s">
         <v>8</v>
       </c>

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390B15EA-8D87-4C3B-8AC8-B236072C4598}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101376E4-1E41-4B68-A02B-45FB77CAE4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
   <si>
     <t>Partido 1</t>
   </si>
@@ -129,6 +129,9 @@
   </si>
   <si>
     <t>Pasa Noruega</t>
+  </si>
+  <si>
+    <t>Pasa Inglaterra</t>
   </si>
 </sst>
 </file>
@@ -265,6 +268,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -272,12 +281,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -627,11 +630,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -659,10 +662,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -672,11 +675,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -704,10 +707,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="3" t="s">
         <v>6</v>
       </c>
@@ -717,11 +720,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -749,10 +752,10 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
@@ -762,11 +765,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -794,20 +797,24 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="3"/>
+      <c r="B16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I16" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -835,8 +842,8 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3"/>
       <c r="I20" s="5" t="s">
         <v>8</v>
@@ -844,11 +851,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -876,8 +883,8 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9"/>
-      <c r="C24" s="10"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="3"/>
       <c r="I24" s="5" t="s">
         <v>8</v>
@@ -885,11 +892,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -917,8 +924,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -926,11 +933,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -958,8 +965,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1391,22 +1398,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101376E4-1E41-4B68-A02B-45FB77CAE4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4EF15C-A400-42E9-B424-7CA09E06FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
   <si>
     <t>Partido 1</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Pasa Inglaterra</t>
+  </si>
+  <si>
+    <t>Pasa España</t>
   </si>
 </sst>
 </file>
@@ -842,9 +845,13 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="C20" s="7"/>
-      <c r="D20" s="3"/>
+      <c r="D20" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I20" s="5" t="s">
         <v>8</v>
       </c>

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D4EF15C-A400-42E9-B424-7CA09E06FC6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A006F5-72F3-4195-A20D-6FB27AFDCAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="34">
   <si>
     <t>Partido 1</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Pasa España</t>
+  </si>
+  <si>
+    <t>Pasa Bélgica</t>
   </si>
 </sst>
 </file>
@@ -271,12 +274,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -284,6 +281,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -633,11 +636,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -665,10 +668,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -678,11 +681,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -710,10 +713,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="3" t="s">
         <v>6</v>
       </c>
@@ -723,11 +726,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -755,10 +758,10 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
@@ -768,11 +771,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -800,10 +803,10 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="3" t="s">
         <v>6</v>
       </c>
@@ -813,11 +816,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -845,10 +848,10 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
@@ -858,11 +861,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -890,20 +893,24 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="6"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="3"/>
+      <c r="B24" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I24" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -931,8 +938,8 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="6"/>
-      <c r="C28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="3"/>
       <c r="I28" s="5" t="s">
         <v>8</v>
@@ -940,11 +947,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -972,8 +979,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="10"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1405,22 +1412,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A006F5-72F3-4195-A20D-6FB27AFDCAA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246759BC-A891-4A20-B1A0-1D54685392BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
   <si>
     <t>Partido 1</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Pasa Bélgica</t>
+  </si>
+  <si>
+    <t>Pasa Argentina</t>
   </si>
 </sst>
 </file>
@@ -274,6 +277,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -281,12 +290,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -636,11 +639,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="10"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -668,10 +671,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -681,11 +684,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="10"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -713,10 +716,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="3" t="s">
         <v>6</v>
       </c>
@@ -726,11 +729,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="10"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -758,10 +761,10 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="7"/>
       <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
@@ -771,11 +774,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -803,10 +806,10 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="3" t="s">
         <v>6</v>
       </c>
@@ -816,11 +819,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -848,10 +851,10 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
@@ -861,11 +864,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="10"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -893,10 +896,10 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="7"/>
       <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
@@ -906,11 +909,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="10"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -938,20 +941,24 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="3"/>
+      <c r="B28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="I28" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -979,8 +986,8 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="9"/>
-      <c r="C32" s="10"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
       <c r="D32" s="3"/>
       <c r="I32" s="5" t="s">
         <v>8</v>
@@ -1412,22 +1419,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">

--- a/Pauta/E03Pauta.xlsx
+++ b/Pauta/E03Pauta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github Clones\Polla Mundial\polla-mundial\Pauta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{246759BC-A891-4A20-B1A0-1D54685392BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C05D6C4-5D43-46A1-AE4F-E6E9730CBA32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12270" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{80BA0768-A233-4C15-9128-A9DFED026552}"/>
   </bookViews>
   <sheets>
     <sheet name="Fase de Grupos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>Partido 1</t>
   </si>
@@ -141,6 +141,9 @@
   </si>
   <si>
     <t>Pasa Argentina</t>
+  </si>
+  <si>
+    <t>Pasa Suiza</t>
   </si>
 </sst>
 </file>
@@ -277,12 +280,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -290,6 +287,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -639,11 +642,11 @@
   <sheetData>
     <row r="1" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="8"/>
       <c r="H2" s="5" t="str">
         <f>"Pasa "&amp;B3</f>
         <v>Pasa Canadá</v>
@@ -671,10 +674,10 @@
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="10"/>
       <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
@@ -684,11 +687,11 @@
     </row>
     <row r="5" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="10"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="8"/>
       <c r="H6" s="5" t="str">
         <f>"Pasa "&amp;B7</f>
         <v>Pasa Paraguay</v>
@@ -716,10 +719,10 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="10"/>
       <c r="D8" s="3" t="s">
         <v>6</v>
       </c>
@@ -729,11 +732,11 @@
     </row>
     <row r="9" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="8"/>
       <c r="H10" s="5" t="str">
         <f>"Pasa "&amp;B11</f>
         <v>Pasa Brasil</v>
@@ -761,10 +764,10 @@
       </c>
     </row>
     <row r="12" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="10"/>
       <c r="D12" s="3" t="s">
         <v>6</v>
       </c>
@@ -774,11 +777,11 @@
     </row>
     <row r="13" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="14" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="8"/>
       <c r="H14" s="5" t="str">
         <f>"Pasa "&amp;B15</f>
         <v>Pasa México</v>
@@ -806,10 +809,10 @@
       </c>
     </row>
     <row r="16" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="10"/>
       <c r="D16" s="3" t="s">
         <v>6</v>
       </c>
@@ -819,11 +822,11 @@
     </row>
     <row r="17" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="8"/>
       <c r="H18" s="5" t="str">
         <f>"Pasa "&amp;B19</f>
         <v>Pasa Portugal</v>
@@ -851,10 +854,10 @@
       </c>
     </row>
     <row r="20" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="10"/>
       <c r="D20" s="3" t="s">
         <v>6</v>
       </c>
@@ -864,11 +867,11 @@
     </row>
     <row r="21" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="22" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="8"/>
       <c r="H22" s="5" t="str">
         <f>"Pasa "&amp;B23</f>
         <v>Pasa Estados Unidos</v>
@@ -896,10 +899,10 @@
       </c>
     </row>
     <row r="24" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="7"/>
+      <c r="C24" s="10"/>
       <c r="D24" s="3" t="s">
         <v>6</v>
       </c>
@@ -909,11 +912,11 @@
     </row>
     <row r="25" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="26" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="8"/>
       <c r="H26" s="5" t="str">
         <f>"Pasa "&amp;B27</f>
         <v>Pasa Argentina</v>
@@ -941,10 +944,10 @@
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="10"/>
       <c r="D28" s="3" t="s">
         <v>6</v>
       </c>
@@ -954,11 +957,11 @@
     </row>
     <row r="29" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="8"/>
       <c r="H30" s="5" t="str">
         <f>"Pasa "&amp;B31</f>
         <v>Pasa Suiza</v>
@@ -986,9 +989,13 @@
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="6"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="3"/>
+      <c r="B32" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="I32" s="5" t="s">
         <v>8</v>
       </c>
@@ -1419,22 +1426,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4 B8 B12 B16 B20 B24 B28 B32" xr:uid="{620C67C7-8AE4-49E4-85F7-B966B2D87176}">
